--- a/tests/fixtures/local_budget.xlsx
+++ b/tests/fixtures/local_budget.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ12"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1594,6 +1594,318 @@
         <is>
           <t>87.02</t>
         </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" t="n">
+        <v>3</v>
+      </c>
+      <c r="F13" t="n">
+        <v>4</v>
+      </c>
+      <c r="G13" t="n">
+        <v>5</v>
+      </c>
+      <c r="H13" t="n">
+        <v>6</v>
+      </c>
+      <c r="I13" t="n">
+        <v>7</v>
+      </c>
+      <c r="J13" t="n">
+        <v>8</v>
+      </c>
+      <c r="K13" t="n">
+        <v>9</v>
+      </c>
+      <c r="L13" t="n">
+        <v>10</v>
+      </c>
+      <c r="M13" t="n">
+        <v>11</v>
+      </c>
+      <c r="N13" t="n">
+        <v>12</v>
+      </c>
+      <c r="O13" t="n">
+        <v>13</v>
+      </c>
+      <c r="P13" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>15</v>
+      </c>
+      <c r="R13" t="n">
+        <v>16</v>
+      </c>
+      <c r="S13" t="n">
+        <v>17</v>
+      </c>
+      <c r="T13" t="n">
+        <v>18</v>
+      </c>
+      <c r="U13" t="n">
+        <v>19</v>
+      </c>
+      <c r="V13" t="n">
+        <v>20</v>
+      </c>
+      <c r="W13" t="n">
+        <v>21</v>
+      </c>
+      <c r="X13" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>23</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>26</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>27</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>30</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>31</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>33</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>35</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>37</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>38</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>39</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>40</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>41</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>42</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>43</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>44</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>45</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>46</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>47</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>48</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>49</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="n">
+        <v>123087687954</v>
+      </c>
+      <c r="D14" t="n">
+        <v>54857611611</v>
+      </c>
+      <c r="E14" t="n">
+        <v>24818473059</v>
+      </c>
+      <c r="F14" t="n">
+        <v>8696426711</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1533277292</v>
+      </c>
+      <c r="H14" t="n">
+        <v>512381608</v>
+      </c>
+      <c r="I14" t="n">
+        <v>273410415</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3997339025</v>
+      </c>
+      <c r="K14" t="n">
+        <v>13171444401</v>
+      </c>
+      <c r="L14" t="n">
+        <v>789367099</v>
+      </c>
+      <c r="M14" t="n">
+        <v>13364764869</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>804706281</v>
+      </c>
+      <c r="P14" t="n">
+        <v>76501771</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>501824117</v>
+      </c>
+      <c r="R14" t="n">
+        <v>27252233279</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3444681366</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2024234933</v>
+      </c>
+      <c r="U14" t="n">
+        <v>15945569</v>
+      </c>
+      <c r="V14" t="n">
+        <v>2990942731</v>
+      </c>
+      <c r="W14" t="n">
+        <v>297915019</v>
+      </c>
+      <c r="X14" t="n">
+        <v>123426088731</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>24457519451</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>23522237583</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1585630338</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>4910057635</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>7866854168</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1915282299</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>3964977848</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>9456017883</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>2367374189</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>2642439758</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>3737291935</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>5215008166</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>30089669484</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>2240285533</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>-544557539</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>19967888413</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>2020611865</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>12697029009</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>4060112287</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>10503618558</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>20179877471</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>13921312310</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>8761915069</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>392250600</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>2977344945</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>157394677</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>27533167165</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>253566362</v>
       </c>
     </row>
   </sheetData>
